--- a/isms-core-framework/A.8-technological-controls/isms-a.8.1-7-18-19-endpoint-security/WKBK/90_workbooks/ISMS-IMP-A.8.1-7-18-19.S4_Privileged_Utilities_20260208.xlsx
+++ b/isms-core-framework/A.8-technological-controls/isms-a.8.1-7-18-19-endpoint-security/WKBK/90_workbooks/ISMS-IMP-A.8.1-7-18-19.S4_Privileged_Utilities_20260208.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>08.02.2026 11:49</t>
+          <t>08.02.2026 12:26</t>
         </is>
       </c>
     </row>
